--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/12_relationships.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/12_relationships.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R34fe73a6b19f4f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Re6628cbbb94d4f80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R3b81da14de704a10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R732a452cada741bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R4f3ae438eda74ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R10f0578634bb47d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allowed Relationships" sheetId="7" r:id="Rff4bbd0866ce4b11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rce5887b225694faf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R9f27bd2d938e4552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rcc7a451bcf4d4cfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R428293149c6e40cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R4c6386c466554915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R5757d3bbe71043e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allowed Relationships" sheetId="7" r:id="R77ac9539027143fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4afed6c5881d481b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd64280676cb54904"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -749,7 +749,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I6" s="80" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Executive Office Workflow Platform supports Executive Office (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -781,7 +781,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I7" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Executive Office owned by Chief Strategy Officer (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J7" s="43" t="str">
         <x:v>Medium</x:v>
@@ -813,7 +813,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I8" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Executive Office Operational Dataset produced by Executive Office Workflow Platform (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J8" s="43" t="str">
         <x:v>Medium</x:v>
@@ -845,7 +845,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I9" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Executive Office Analytics Mart consumes Executive Office Operational Dataset (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J9" s="43" t="str">
         <x:v>Medium</x:v>
@@ -877,7 +877,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I10" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Executive Office Workflow Platform feeds Executive Office Analytics Mart (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J10" s="43" t="str">
         <x:v>Medium</x:v>
@@ -909,7 +909,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I11" s="81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Executive Office Analytics Mart integrates with Executive Office Reporting Workspace (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J11" s="43" t="str">
         <x:v>Medium</x:v>
@@ -941,7 +941,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I12" s="82" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Executive Office Reporting Workspace depends on Executive Office Workflow Platform (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J12" s="45" t="str">
         <x:v>Medium</x:v>
@@ -973,7 +973,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I13" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Executive Office Workflow Platform hosted on Executive Office Primary Midwest Data Center Hosting Segment (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J13" t="str">
         <x:v>Medium</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I14" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Executive Office Workflow Platform hosted in Primary Midwest Data Center (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J14" t="str">
         <x:v>Medium</x:v>
@@ -1037,7 +1037,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I15" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks on AWS Lakehouse target for Executive Office Operational Dataset (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J15" t="str">
         <x:v>Medium</x:v>
@@ -1069,7 +1069,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I16" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Executive Office governed by Enterprise Strategy governance council (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J16" t="str">
         <x:v>Medium</x:v>
@@ -1101,7 +1101,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I17" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Enterprise profile and corporate priorities program funded by Chief Strategy Officer (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J17" t="str">
         <x:v>Medium</x:v>
@@ -1133,7 +1133,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I18" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Databricks on AWS Lakehouse replaces candidate legacy Executive Office Operational Dataset (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J18" t="str">
         <x:v>Medium</x:v>
@@ -1165,7 +1165,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I19" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Executive Office used by Executive Office Analyst / Steward (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J19" t="str">
         <x:v>Medium</x:v>
@@ -1197,7 +1197,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I20" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Executive Office Operational Dataset part of Enterprise profile and corporate priorities modernization and readiness program (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J20" t="str">
         <x:v>Medium</x:v>
@@ -1229,7 +1229,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I21" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Oracle provides Executive Office Workflow Platform (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J21" t="str">
         <x:v>Medium</x:v>
@@ -1261,7 +1261,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I22" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Executive Office measured by Executive Office cycle time (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J22" t="str">
         <x:v>Medium</x:v>
@@ -1293,7 +1293,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01</x:v>
       </x:c>
       <x:c r="I23" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Executive Office has risk Executive Office data lineage and definition risk (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J23" t="str">
         <x:v>Medium</x:v>
@@ -1325,7 +1325,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I24" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Epic Hyperspace supports Provider Operations (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J24" t="str">
         <x:v>Medium</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I25" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider Operations owned by CMO (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J25" t="str">
         <x:v>Medium</x:v>
@@ -1389,7 +1389,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I26" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Provider Operations Operational Dataset produced by Epic Hyperspace (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J26" t="str">
         <x:v>Medium</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I27" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Epic Clarity consumes Provider Operations Operational Dataset (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J27" t="str">
         <x:v>Medium</x:v>
@@ -1453,7 +1453,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I28" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Epic Hyperspace feeds Provider Operations Analytics Mart (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J28" t="str">
         <x:v>Medium</x:v>
@@ -1485,7 +1485,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I29" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Epic Clarity integrates with Epic Caboodle (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J29" t="str">
         <x:v>Medium</x:v>
@@ -1517,7 +1517,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I30" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Epic Caboodle depends on Epic Hyperspace (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J30" t="str">
         <x:v>Medium</x:v>
@@ -1549,7 +1549,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I31" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Epic Hyperspace hosted on Provider Operations Primary Midwest Data Center Hosting Segment (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J31" t="str">
         <x:v>Medium</x:v>
@@ -1581,7 +1581,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I32" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Epic Hyperspace hosted in Primary Midwest Data Center (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J32" t="str">
         <x:v>Medium</x:v>
@@ -1613,7 +1613,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I33" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Databricks on AWS Lakehouse target for Provider Operations Operational Dataset (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J33" t="str">
         <x:v>Medium</x:v>
@@ -1645,7 +1645,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I34" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Provider Operations governed by Clinical Operations governance council (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J34" t="str">
         <x:v>Medium</x:v>
@@ -1677,7 +1677,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I35" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider / clinical operations program funded by CMO (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J35" t="str">
         <x:v>Medium</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I36" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse replaces candidate legacy Provider Operations Operational Dataset (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J36" t="str">
         <x:v>Medium</x:v>
@@ -1741,7 +1741,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I37" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Provider Operations used by Provider Operations Analyst / Steward (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J37" t="str">
         <x:v>Medium</x:v>
@@ -1773,7 +1773,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I38" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Provider Operations Operational Dataset part of Provider / clinical operations modernization and readiness program (record 33), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J38" t="str">
         <x:v>Medium</x:v>
@@ -1805,7 +1805,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I39" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Workday provides Epic Hyperspace (record 34) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J39" t="str">
         <x:v>Medium</x:v>
@@ -1837,7 +1837,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I40" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider Operations measured by Provider Operations cycle time (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J40" t="str">
         <x:v>Medium</x:v>
@@ -1869,7 +1869,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01</x:v>
       </x:c>
       <x:c r="I41" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Provider Operations has risk Provider Operations data lineage and definition risk (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J41" t="str">
         <x:v>Medium</x:v>
@@ -1901,7 +1901,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I42" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Claims Administration Platform supports Claims Operations (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J42" t="str">
         <x:v>Medium</x:v>
@@ -1933,7 +1933,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I43" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Claims Operations owned by Health Plan COO (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J43" t="str">
         <x:v>Medium</x:v>
@@ -1965,7 +1965,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I44" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Claims Operations Operational Dataset produced by Claims Administration Platform (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J44" t="str">
         <x:v>Medium</x:v>
@@ -1997,7 +1997,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I45" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Payment Rules Engine consumes Claims Operations Operational Dataset (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J45" t="str">
         <x:v>Medium</x:v>
@@ -2029,7 +2029,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I46" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Claims Administration Platform feeds Claims Operations Analytics Mart (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J46" t="str">
         <x:v>Medium</x:v>
@@ -2061,7 +2061,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I47" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Claims Payment Rules Engine integrates with Claims Inquiry CRM Adapter (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J47" t="str">
         <x:v>Medium</x:v>
@@ -2093,7 +2093,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I48" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Claims Inquiry CRM Adapter depends on Claims Administration Platform (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J48" t="str">
         <x:v>Medium</x:v>
@@ -2125,7 +2125,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I49" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Claims Administration Platform hosted on Claims Operations Primary Midwest Data Center Hosting Segment (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J49" t="str">
         <x:v>Medium</x:v>
@@ -2157,7 +2157,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Administration Platform hosted in Primary Midwest Data Center (record 45) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J50" t="str">
         <x:v>Medium</x:v>
@@ -2189,7 +2189,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse target for Claims Operations Operational Dataset (record 46) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J51" t="str">
         <x:v>Medium</x:v>
@@ -2221,7 +2221,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Claims Operations governed by Health Plan Operations governance council (record 47) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J52" t="str">
         <x:v>Medium</x:v>
@@ -2253,7 +2253,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I53" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Payer / claims operations program funded by Health Plan COO (record 48), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J53" t="str">
         <x:v>Medium</x:v>
@@ -2285,7 +2285,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks on AWS Lakehouse replaces candidate legacy Claims Operations Operational Dataset (record 49) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J54" t="str">
         <x:v>Medium</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I55" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Operations used by Claims Operations Analyst / Steward (record 50) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J55" t="str">
         <x:v>Medium</x:v>
@@ -2349,7 +2349,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I56" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Claims Operations Operational Dataset part of Payer / claims operations modernization and readiness program (record 51) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J56" t="str">
         <x:v>Medium</x:v>
@@ -2381,7 +2381,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks provides Claims Administration Platform (record 52) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J57" t="str">
         <x:v>Medium</x:v>
@@ -2413,7 +2413,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I58" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Claims Operations measured by Claims Operations cycle time (record 53), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J58" t="str">
         <x:v>Medium</x:v>
@@ -2445,7 +2445,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Claims Operations has risk Claims Operations data lineage and definition risk (record 54) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J59" t="str">
         <x:v>Medium</x:v>
@@ -2477,7 +2477,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I60" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Eligibility and Benefits Workflow Platform supports Eligibility and Benefits (record 55) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J60" t="str">
         <x:v>Medium</x:v>
@@ -2509,7 +2509,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I61" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Eligibility and Benefits owned by VP Benefits Operations (record 56) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J61" t="str">
         <x:v>Medium</x:v>
@@ -2541,7 +2541,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Eligibility Benefits Operational Dataset produced by Eligibility and Benefits Workflow Platform (record 57) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J62" t="str">
         <x:v>Medium</x:v>
@@ -2573,7 +2573,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I63" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Eligibility and Benefits Analytics Mart consumes Eligibility Benefits Operational Dataset (record 58), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J63" t="str">
         <x:v>Medium</x:v>
@@ -2605,7 +2605,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I64" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Eligibility and Benefits Workflow Platform feeds Eligibility Benefits Analytics Mart (record 59) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J64" t="str">
         <x:v>Medium</x:v>
@@ -2637,7 +2637,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I65" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Eligibility and Benefits Analytics Mart integrates with Eligibility and Benefits Reporting Workspace (record 60) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J65" t="str">
         <x:v>Medium</x:v>
@@ -2669,7 +2669,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I66" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Eligibility and Benefits Reporting Workspace depends on Eligibility and Benefits Workflow Platform (record 61) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J66" t="str">
         <x:v>Medium</x:v>
@@ -2701,7 +2701,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I67" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Eligibility and Benefits Workflow Platform hosted on Eligibility and Benefits Primary Midwest Data Center Hosting Segment (record 62) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J67" t="str">
         <x:v>Medium</x:v>
@@ -2733,7 +2733,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I68" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Eligibility and Benefits Workflow Platform hosted in Primary Midwest Data Center (record 63), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J68" t="str">
         <x:v>Medium</x:v>
@@ -2765,7 +2765,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks on AWS Lakehouse target for Eligibility Benefits Operational Dataset (record 64) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J69" t="str">
         <x:v>Medium</x:v>
@@ -2797,7 +2797,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Eligibility and Benefits governed by Health Plan Operations governance council (record 65) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J70" t="str">
         <x:v>Medium</x:v>
@@ -2829,7 +2829,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I71" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Eligibility / benefits program funded by VP Benefits Operations (record 66) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J71" t="str">
         <x:v>Medium</x:v>
@@ -2861,7 +2861,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse replaces candidate legacy Eligibility Benefits Operational Dataset (record 67) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J72" t="str">
         <x:v>Medium</x:v>
@@ -2893,7 +2893,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Eligibility and Benefits used by Eligibility and Benefits Analyst / Steward (record 68), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J73" t="str">
         <x:v>Medium</x:v>
@@ -2925,7 +2925,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I74" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Eligibility Benefits Operational Dataset part of Eligibility / benefits modernization and readiness program (record 69) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J74" t="str">
         <x:v>Medium</x:v>
@@ -2957,7 +2957,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for AWS provides Eligibility and Benefits Workflow Platform (record 70) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J75" t="str">
         <x:v>Medium</x:v>
@@ -2989,7 +2989,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Eligibility and Benefits measured by Eligibility and Benefits cycle time (record 71) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J76" t="str">
         <x:v>Medium</x:v>
@@ -3021,7 +3021,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Eligibility and Benefits has risk Eligibility and Benefits data lineage and definition risk (record 72) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J77" t="str">
         <x:v>Medium</x:v>
@@ -3053,7 +3053,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Prior Authorization and UM Workflow Platform supports Prior Authorization and UM (record 73), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J78" t="str">
         <x:v>Medium</x:v>
@@ -3085,7 +3085,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Prior Authorization and UM owned by VP Utilization Management (record 74) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J79" t="str">
         <x:v>Medium</x:v>
@@ -3117,7 +3117,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization UM Operational Dataset produced by Prior Authorization and UM Workflow Platform (record 75) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J80" t="str">
         <x:v>Medium</x:v>
@@ -3149,7 +3149,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Prior Authorization and UM Analytics Mart consumes Prior Authorization UM Operational Dataset (record 76) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J81" t="str">
         <x:v>Medium</x:v>
@@ -3181,7 +3181,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I82" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Prior Authorization and UM Workflow Platform feeds Prior Authorization UM Analytics Mart (record 77) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J82" t="str">
         <x:v>Medium</x:v>
@@ -3213,7 +3213,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I83" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Prior Authorization and UM Analytics Mart integrates with Prior Authorization and UM Reporting Workspace (record 78), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J83" t="str">
         <x:v>Medium</x:v>
@@ -3245,7 +3245,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I84" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Prior Authorization and UM Reporting Workspace depends on Prior Authorization and UM Workflow Platform (record 79) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J84" t="str">
         <x:v>Medium</x:v>
@@ -3277,7 +3277,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM Workflow Platform hosted on Prior Authorization and UM Primary Midwest Data Center Hosting Segment (record 80) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J85" t="str">
         <x:v>Medium</x:v>
@@ -3309,7 +3309,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I86" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Prior Authorization and UM Workflow Platform hosted in Primary Midwest Data Center (record 81) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J86" t="str">
         <x:v>Medium</x:v>
@@ -3341,7 +3341,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I87" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse target for Prior Authorization UM Operational Dataset (record 82) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J87" t="str">
         <x:v>Medium</x:v>
@@ -3373,7 +3373,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I88" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Prior Authorization and UM governed by Utilization Management governance council (record 83), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J88" t="str">
         <x:v>Medium</x:v>
@@ -3405,7 +3405,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I89" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Prior authorization / utilization management program funded by VP Utilization Management (record 84) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J89" t="str">
         <x:v>Medium</x:v>
@@ -3437,7 +3437,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks on AWS Lakehouse replaces candidate legacy Prior Authorization UM Operational Dataset (record 85) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J90" t="str">
         <x:v>Medium</x:v>
@@ -3469,7 +3469,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I91" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Prior Authorization and UM used by Prior Authorization and UM Analyst / Steward (record 86) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J91" t="str">
         <x:v>Medium</x:v>
@@ -3501,7 +3501,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Prior Authorization UM Operational Dataset part of Prior authorization / utilization management modernization and readiness program (record 87) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J92" t="str">
         <x:v>Medium</x:v>
@@ -3533,7 +3533,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Tableau provides Prior Authorization and UM Workflow Platform (record 88), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J93" t="str">
         <x:v>Medium</x:v>
@@ -3565,7 +3565,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I94" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Prior Authorization and UM measured by Prior Authorization and UM cycle time (record 89) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J94" t="str">
         <x:v>Medium</x:v>
@@ -3597,7 +3597,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01</x:v>
       </x:c>
       <x:c r="I95" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM has risk Prior Authorization and UM data lineage and definition risk (record 90) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J95" t="str">
         <x:v>Medium</x:v>
@@ -3623,13 +3623,13 @@
         <x:v>Business Function</x:v>
       </x:c>
       <x:c r="G96" t="str">
-        <x:v>Genesys Cloud Contact Center supports member calls, CRM case management, next-best-action workflows.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="H96" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.</x:v>
       </x:c>
       <x:c r="I96" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Genesys Cloud Contact Center supports Contact Center and Member Service (record 91) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J96" t="str">
         <x:v>Medium</x:v>
@@ -3655,13 +3655,13 @@
         <x:v>Owner / Executive Role</x:v>
       </x:c>
       <x:c r="G97" t="str">
-        <x:v>Chief Experience Officer is accountable for Contact Center and Member Service evidence and readiness.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="H97" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.</x:v>
       </x:c>
       <x:c r="I97" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center and Member Service owned by Chief Experience Officer (record 92) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J97" t="str">
         <x:v>Medium</x:v>
@@ -3687,13 +3687,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G98" t="str">
-        <x:v>Contact Center Member Service Operational Dataset is produced or sourced from Genesys Cloud Contact Center.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="H98" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.</x:v>
       </x:c>
       <x:c r="I98" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center Member Service Operational Dataset produced by Genesys Cloud Contact Center (record 93) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J98" t="str">
         <x:v>Medium</x:v>
@@ -3719,13 +3719,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G99" t="str">
-        <x:v>Salesforce Health Cloud CRM consumes Contact Center Member Service Operational Dataset for analytics/workflow support.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="H99" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Knowledge article export with duplicate and stale article flags.</x:v>
       </x:c>
       <x:c r="I99" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Salesforce Health Cloud CRM consumes Contact Center Member Service Operational Dataset (record 94) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J99" t="str">
         <x:v>Medium</x:v>
@@ -3751,13 +3751,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G100" t="str">
-        <x:v>Genesys Cloud Contact Center feeds Contact Center Member Service Analytics Mart through batch/API/interface flows that require lineage validation.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="H100" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="I100" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Genesys Cloud Contact Center feeds Contact Center Member Service Analytics Mart (record 95) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J100" t="str">
         <x:v>Medium</x:v>
@@ -3789,7 +3789,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I101" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Salesforce Health Cloud CRM integrates with Call Transcript Lake Landing Zone (record 96) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J101" t="str">
         <x:v>Medium</x:v>
@@ -3815,13 +3815,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G102" t="str">
-        <x:v>Call Transcript Lake Landing Zone depends on Genesys Cloud Contact Center for source data, workflow handoff, or identity/transaction context.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="H102" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.</x:v>
       </x:c>
       <x:c r="I102" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Call Transcript Lake Landing Zone depends on Genesys Cloud Contact Center (record 97) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J102" t="str">
         <x:v>Medium</x:v>
@@ -3847,13 +3847,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G103" t="str">
-        <x:v>Genesys Cloud Contact Center is hosted on or materially depends on the Contact Center and Member Service hosting segment.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="H103" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.</x:v>
       </x:c>
       <x:c r="I103" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Genesys Cloud Contact Center hosted on Contact Center and Member Service Primary Midwest Data Center Hosting Segment (record 98) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J103" t="str">
         <x:v>Medium</x:v>
@@ -3879,13 +3879,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G104" t="str">
-        <x:v>Genesys Cloud Contact Center has current or dependent hosting in Primary Midwest Data Center.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="H104" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Knowledge article export with duplicate and stale article flags.</x:v>
       </x:c>
       <x:c r="I104" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Genesys Cloud Contact Center hosted in Primary Midwest Data Center (record 99) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J104" t="str">
         <x:v>Medium</x:v>
@@ -3911,13 +3911,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G105" t="str">
-        <x:v>Databricks on AWS Lakehouse is the target path for governed modernization of Contact Center Member Service Operational Dataset.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="H105" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="I105" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse target for Contact Center Member Service Operational Dataset (record 100) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J105" t="str">
         <x:v>Medium</x:v>
@@ -3943,13 +3943,13 @@
         <x:v>Governance Forum</x:v>
       </x:c>
       <x:c r="G106" t="str">
-        <x:v>Member Experience governance council should validate evidence, exceptions, metrics, and promotion readiness.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="H106" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.</x:v>
       </x:c>
       <x:c r="I106" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center and Member Service governed by Member Experience governance council (record 101) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J106" t="str">
         <x:v>Medium</x:v>
@@ -3981,7 +3981,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
       </x:c>
       <x:c r="I107" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Member experience / contact center program funded by Chief Experience Officer (record 102) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J107" t="str">
         <x:v>Medium</x:v>
@@ -4007,13 +4007,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G108" t="str">
-        <x:v>Contact Center Member Service Operational Dataset is a candidate legacy/fragmented asset to be rationalized or certified through Databricks on AWS Lakehouse.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="H108" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.</x:v>
       </x:c>
       <x:c r="I108" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse replaces candidate legacy Contact Center Member Service Operational Dataset (record 103) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J108" t="str">
         <x:v>Medium</x:v>
@@ -4039,13 +4039,13 @@
         <x:v>Workforce Role</x:v>
       </x:c>
       <x:c r="G109" t="str">
-        <x:v>Contact Center and Member Service analysts and stewards use this context for reporting, reconciliation, and readiness checks.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="H109" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Knowledge article export with duplicate and stale article flags.</x:v>
       </x:c>
       <x:c r="I109" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center and Member Service used by Contact Center and Member Service Analyst / Steward (record 104) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J109" t="str">
         <x:v>Medium</x:v>
@@ -4071,13 +4071,13 @@
         <x:v>Program / Initiative</x:v>
       </x:c>
       <x:c r="G110" t="str">
-        <x:v>Contact Center Member Service Operational Dataset is in scope for Member experience / contact center modernization, validation, or context-readiness work.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="H110" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="I110" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center Member Service Operational Dataset part of Member experience / contact center modernization and readiness program (record 105) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J110" t="str">
         <x:v>Medium</x:v>
@@ -4103,13 +4103,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G111" t="str">
-        <x:v>ServiceNow provides, supports, or contracts around Genesys Cloud Contact Center.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="H111" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.</x:v>
       </x:c>
       <x:c r="I111" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate ServiceNow provides Genesys Cloud Contact Center (record 106) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J111" t="str">
         <x:v>Medium</x:v>
@@ -4135,13 +4135,13 @@
         <x:v>Metric / Outcome</x:v>
       </x:c>
       <x:c r="G112" t="str">
-        <x:v>Contact Center and Member Service cycle time measures Contact Center and Member Service performance.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="H112" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.</x:v>
       </x:c>
       <x:c r="I112" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center and Member Service measured by Contact Center and Member Service cycle time (record 107) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J112" t="str">
         <x:v>Medium</x:v>
@@ -4167,13 +4167,13 @@
         <x:v>Risk / Control</x:v>
       </x:c>
       <x:c r="G113" t="str">
-        <x:v>Contact Center and Member Service has a known evidence/lineage risk until validation is complete.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="H113" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01</x:v>
+        <x:v>Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.</x:v>
       </x:c>
       <x:c r="I113" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Contact Center and Member Service has risk Contact Center and Member Service data lineage and definition risk (record 108) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J113" t="str">
         <x:v>Medium</x:v>
@@ -4205,7 +4205,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I114" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Revenue Cycle Operations Workflow Platform supports Revenue Cycle Operations (record 109) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J114" t="str">
         <x:v>Medium</x:v>
@@ -4237,7 +4237,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I115" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Revenue Cycle Operations owned by Revenue Cycle Leader (record 110) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J115" t="str">
         <x:v>Medium</x:v>
@@ -4269,7 +4269,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I116" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Revenue Cycle Operations Operational Dataset produced by Revenue Cycle Operations Workflow Platform (record 111) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J116" t="str">
         <x:v>Medium</x:v>
@@ -4301,7 +4301,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I117" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Revenue Cycle Operations Analytics Mart consumes Revenue Cycle Operations Operational Dataset (record 112) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J117" t="str">
         <x:v>Medium</x:v>
@@ -4333,7 +4333,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I118" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Revenue Cycle Operations Workflow Platform feeds Revenue Cycle Operations Analytics Mart (record 113), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J118" t="str">
         <x:v>Medium</x:v>
@@ -4365,7 +4365,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I119" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Revenue Cycle Operations Analytics Mart integrates with Revenue Cycle Operations Reporting Workspace (record 114) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J119" t="str">
         <x:v>Medium</x:v>
@@ -4397,7 +4397,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I120" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Revenue Cycle Operations Reporting Workspace depends on Revenue Cycle Operations Workflow Platform (record 115) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J120" t="str">
         <x:v>Medium</x:v>
@@ -4429,7 +4429,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I121" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Revenue Cycle Operations Workflow Platform hosted on Revenue Cycle Operations Primary Midwest Data Center Hosting Segment (record 116) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J121" t="str">
         <x:v>Medium</x:v>
@@ -4461,7 +4461,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I122" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Revenue Cycle Operations Workflow Platform hosted in Primary Midwest Data Center (record 117) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J122" t="str">
         <x:v>Medium</x:v>
@@ -4493,7 +4493,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I123" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Databricks on AWS Lakehouse target for Revenue Cycle Operations Operational Dataset (record 118), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J123" t="str">
         <x:v>Medium</x:v>
@@ -4525,7 +4525,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I124" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Revenue Cycle Operations governed by Revenue Cycle governance council (record 119) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J124" t="str">
         <x:v>Medium</x:v>
@@ -4557,7 +4557,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I125" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Revenue cycle program funded by Revenue Cycle Leader (record 120) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J125" t="str">
         <x:v>Medium</x:v>
@@ -4589,7 +4589,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I126" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse replaces candidate legacy Revenue Cycle Operations Operational Dataset (record 121) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J126" t="str">
         <x:v>Medium</x:v>
@@ -4621,7 +4621,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I127" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Revenue Cycle Operations used by Revenue Cycle Operations Analyst / Steward (record 122) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J127" t="str">
         <x:v>Medium</x:v>
@@ -4653,7 +4653,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I128" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Revenue Cycle Operations Operational Dataset part of Revenue cycle modernization and readiness program (record 123), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J128" t="str">
         <x:v>Medium</x:v>
@@ -4685,7 +4685,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I129" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Informatica provides Revenue Cycle Operations Workflow Platform (record 124) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J129" t="str">
         <x:v>Medium</x:v>
@@ -4717,7 +4717,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I130" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Revenue Cycle Operations measured by Revenue Cycle Operations cycle time (record 125) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J130" t="str">
         <x:v>Medium</x:v>
@@ -4749,7 +4749,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01</x:v>
       </x:c>
       <x:c r="I131" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Revenue Cycle Operations has risk Revenue Cycle Operations data lineage and definition risk (record 126) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J131" t="str">
         <x:v>Medium</x:v>
@@ -4775,13 +4775,13 @@
         <x:v>Business Function</x:v>
       </x:c>
       <x:c r="G132" t="str">
-        <x:v>Oracle ERP Finance supports GL/AP/AR/budget/vendor spend reporting, close analytics, FP&amp;A dashboards.</x:v>
+        <x:v>Finance Analytics relationship: Vendor spend differs across AP, procurement, and contract repository extracts, so sourcing questions need a reconciled vendor-master rule before Source uses the data.</x:v>
       </x:c>
       <x:c r="H132" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.</x:v>
       </x:c>
       <x:c r="I132" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Oracle ERP Finance supports Finance Analytics (record 127) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J132" t="str">
         <x:v>Medium</x:v>
@@ -4807,13 +4807,13 @@
         <x:v>Owner / Executive Role</x:v>
       </x:c>
       <x:c r="G133" t="str">
-        <x:v>CFO is accountable for Finance Analytics evidence and readiness.</x:v>
+        <x:v>Finance Analytics relationship: FP&amp;A trusts 42 certified dashboards, but business-unit teams still use 300+ Excel extracts copied from legacy Tableau views.</x:v>
       </x:c>
       <x:c r="H133" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.</x:v>
       </x:c>
       <x:c r="I133" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Finance Analytics owned by CFO (record 128) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J133" t="str">
         <x:v>Medium</x:v>
@@ -4839,13 +4839,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G134" t="str">
-        <x:v>Finance Mart GL AP AR Subject Area is produced or sourced from Oracle ERP Finance.</x:v>
+        <x:v>Finance Analytics relationship: Informatica job failures are resolved manually because the finance mart lacks clear lineage from Oracle ERP subledger jobs to report-level consumers.</x:v>
       </x:c>
       <x:c r="H134" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Tableau and Power BI finance dashboard inventory with certified vs shadow-report split.</x:v>
       </x:c>
       <x:c r="I134" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Finance Mart GL AP AR Subject Area produced by Oracle ERP Finance (record 129) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J134" t="str">
         <x:v>Medium</x:v>
@@ -4871,13 +4871,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G135" t="str">
-        <x:v>SQL Server Finance Mart consumes Finance Mart GL AP AR Subject Area for analytics/workflow support.</x:v>
+        <x:v>Finance Analytics relationship: Databricks Finance Gold is the target path, but cost-center hierarchy, vendor master harmonization, and audit signoff are unresolved.</x:v>
       </x:c>
       <x:c r="H135" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Finance Gold Data Product design notes for Databricks target certification.</x:v>
       </x:c>
       <x:c r="I135" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate SQL Server Finance Mart consumes Finance Mart GL AP AR Subject Area (record 130) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J135" t="str">
         <x:v>Medium</x:v>
@@ -4903,13 +4903,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G136" t="str">
-        <x:v>Oracle ERP Finance feeds Vendor Spend and Contract Analytics Dataset through batch/API/interface flows that require lineage validation.</x:v>
+        <x:v>Finance Analytics relationship: Month-end close dashboards slow down because 38 priority reports refresh from five SQL Server finance schemas during the same overnight load window.</x:v>
       </x:c>
       <x:c r="H136" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.</x:v>
       </x:c>
       <x:c r="I136" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Oracle ERP Finance feeds Vendor Spend and Contract Analytics Dataset (record 131) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J136" t="str">
         <x:v>Medium</x:v>
@@ -4935,13 +4935,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G137" t="str">
-        <x:v>SQL Server Finance Mart integrates with Netezza Finance Subject Area for workflow, reporting, or exception handling.</x:v>
+        <x:v>Finance Analytics relationship: Vendor spend differs across AP, procurement, and contract repository extracts, so sourcing questions need a reconciled vendor-master rule before Source uses the data.</x:v>
       </x:c>
       <x:c r="H137" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.</x:v>
       </x:c>
       <x:c r="I137" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate SQL Server Finance Mart integrates with Netezza Finance Subject Area (record 132) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J137" t="str">
         <x:v>Medium</x:v>
@@ -4967,13 +4967,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G138" t="str">
-        <x:v>Netezza Finance Subject Area depends on Oracle ERP Finance for source data, workflow handoff, or identity/transaction context.</x:v>
+        <x:v>Finance Analytics relationship: FP&amp;A trusts 42 certified dashboards, but business-unit teams still use 300+ Excel extracts copied from legacy Tableau views.</x:v>
       </x:c>
       <x:c r="H138" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.</x:v>
       </x:c>
       <x:c r="I138" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Netezza Finance Subject Area depends on Oracle ERP Finance (record 133) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J138" t="str">
         <x:v>Medium</x:v>
@@ -4999,13 +4999,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G139" t="str">
-        <x:v>Oracle ERP Finance is hosted on or materially depends on the Finance Analytics hosting segment.</x:v>
+        <x:v>Finance Analytics relationship: Informatica job failures are resolved manually because the finance mart lacks clear lineage from Oracle ERP subledger jobs to report-level consumers.</x:v>
       </x:c>
       <x:c r="H139" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Tableau and Power BI finance dashboard inventory with certified vs shadow-report split.</x:v>
       </x:c>
       <x:c r="I139" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Oracle ERP Finance hosted on Finance Analytics Primary Midwest Data Center Hosting Segment (record 134) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J139" t="str">
         <x:v>Medium</x:v>
@@ -5031,13 +5031,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G140" t="str">
-        <x:v>Oracle ERP Finance has current or dependent hosting in Primary Midwest Data Center.</x:v>
+        <x:v>Finance Analytics relationship: Databricks Finance Gold is the target path, but cost-center hierarchy, vendor master harmonization, and audit signoff are unresolved.</x:v>
       </x:c>
       <x:c r="H140" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Finance Gold Data Product design notes for Databricks target certification.</x:v>
       </x:c>
       <x:c r="I140" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Oracle ERP Finance hosted in Primary Midwest Data Center (record 135) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J140" t="str">
         <x:v>Medium</x:v>
@@ -5063,13 +5063,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G141" t="str">
-        <x:v>Databricks on AWS Lakehouse is the target path for governed modernization of Finance Mart GL AP AR Subject Area.</x:v>
+        <x:v>Finance Analytics relationship: Month-end close dashboards slow down because 38 priority reports refresh from five SQL Server finance schemas during the same overnight load window.</x:v>
       </x:c>
       <x:c r="H141" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.</x:v>
       </x:c>
       <x:c r="I141" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse target for Finance Mart GL AP AR Subject Area (record 136) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J141" t="str">
         <x:v>Medium</x:v>
@@ -5095,13 +5095,13 @@
         <x:v>Governance Forum</x:v>
       </x:c>
       <x:c r="G142" t="str">
-        <x:v>Finance and Actuarial governance council should validate evidence, exceptions, metrics, and promotion readiness.</x:v>
+        <x:v>Finance Analytics relationship: Vendor spend differs across AP, procurement, and contract repository extracts, so sourcing questions need a reconciled vendor-master rule before Source uses the data.</x:v>
       </x:c>
       <x:c r="H142" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.</x:v>
       </x:c>
       <x:c r="I142" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Finance Analytics governed by Finance and Actuarial governance council (record 137) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J142" t="str">
         <x:v>Medium</x:v>
@@ -5133,7 +5133,7 @@
         <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I143" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Finance analytics program funded by CFO (record 138), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J143" t="str">
         <x:v>Medium</x:v>
@@ -5159,13 +5159,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G144" t="str">
-        <x:v>Finance Mart GL AP AR Subject Area is a candidate legacy/fragmented asset to be rationalized or certified through Databricks on AWS Lakehouse.</x:v>
+        <x:v>Finance Analytics relationship: Informatica job failures are resolved manually because the finance mart lacks clear lineage from Oracle ERP subledger jobs to report-level consumers.</x:v>
       </x:c>
       <x:c r="H144" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Tableau and Power BI finance dashboard inventory with certified vs shadow-report split.</x:v>
       </x:c>
       <x:c r="I144" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse replaces candidate legacy Finance Mart GL AP AR Subject Area (record 139) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J144" t="str">
         <x:v>Medium</x:v>
@@ -5191,13 +5191,13 @@
         <x:v>Workforce Role</x:v>
       </x:c>
       <x:c r="G145" t="str">
-        <x:v>Finance Analytics analysts and stewards use this context for reporting, reconciliation, and readiness checks.</x:v>
+        <x:v>Finance Analytics relationship: Databricks Finance Gold is the target path, but cost-center hierarchy, vendor master harmonization, and audit signoff are unresolved.</x:v>
       </x:c>
       <x:c r="H145" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Finance Gold Data Product design notes for Databricks target certification.</x:v>
       </x:c>
       <x:c r="I145" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Finance Analytics used by Finance Analytics Analyst / Steward (record 140) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J145" t="str">
         <x:v>Medium</x:v>
@@ -5223,13 +5223,13 @@
         <x:v>Program / Initiative</x:v>
       </x:c>
       <x:c r="G146" t="str">
-        <x:v>Finance Mart GL AP AR Subject Area is in scope for Finance analytics modernization, validation, or context-readiness work.</x:v>
+        <x:v>Finance Analytics relationship: Month-end close dashboards slow down because 38 priority reports refresh from five SQL Server finance schemas during the same overnight load window.</x:v>
       </x:c>
       <x:c r="H146" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.</x:v>
       </x:c>
       <x:c r="I146" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Finance Mart GL AP AR Subject Area part of Finance analytics modernization and readiness program (record 141) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J146" t="str">
         <x:v>Medium</x:v>
@@ -5255,13 +5255,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G147" t="str">
-        <x:v>Tableau provides, supports, or contracts around Oracle ERP Finance.</x:v>
+        <x:v>Finance Analytics relationship: Vendor spend differs across AP, procurement, and contract repository extracts, so sourcing questions need a reconciled vendor-master rule before Source uses the data.</x:v>
       </x:c>
       <x:c r="H147" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.</x:v>
       </x:c>
       <x:c r="I147" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Tableau provides Oracle ERP Finance (record 142) against Finance Analytics evidence: inconsistent vendor spend definitions; confirm Databricks Finance Gold certification owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J147" t="str">
         <x:v>Medium</x:v>
@@ -5287,13 +5287,13 @@
         <x:v>Metric / Outcome</x:v>
       </x:c>
       <x:c r="G148" t="str">
-        <x:v>Finance Analytics cycle time measures Finance Analytics performance.</x:v>
+        <x:v>Finance Analytics relationship: FP&amp;A trusts 42 certified dashboards, but business-unit teams still use 300+ Excel extracts copied from legacy Tableau views.</x:v>
       </x:c>
       <x:c r="H148" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.</x:v>
       </x:c>
       <x:c r="I148" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Finance Analytics measured by Finance Analytics cycle time (record 143) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J148" t="str">
         <x:v>Medium</x:v>
@@ -5319,13 +5319,13 @@
         <x:v>Risk / Control</x:v>
       </x:c>
       <x:c r="G149" t="str">
-        <x:v>Finance Analytics has a known evidence/lineage risk until validation is complete.</x:v>
+        <x:v>Finance Analytics relationship: Informatica job failures are resolved manually because the finance mart lacks clear lineage from Oracle ERP subledger jobs to report-level consumers.</x:v>
       </x:c>
       <x:c r="H149" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01</x:v>
+        <x:v>Tableau and Power BI finance dashboard inventory with certified vs shadow-report split.</x:v>
       </x:c>
       <x:c r="I149" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Finance Analytics has risk Finance Analytics data lineage and definition risk (record 144) against Finance Analytics evidence: incomplete lineage from ERP to BI; confirm cost-center hierarchy stewardship owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J149" t="str">
         <x:v>Medium</x:v>
@@ -5357,7 +5357,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I150" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Workforce Analytics Workflow Platform supports Workforce Analytics (record 145) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J150" t="str">
         <x:v>Medium</x:v>
@@ -5389,7 +5389,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I151" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Workforce Analytics owned by CHRO (record 146) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J151" t="str">
         <x:v>Medium</x:v>
@@ -5421,7 +5421,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I152" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Workforce Analytics Operational Dataset produced by Workforce Analytics Workflow Platform (record 147) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J152" t="str">
         <x:v>Medium</x:v>
@@ -5453,7 +5453,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I153" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Workforce Analytics Analytics Mart consumes Workforce Analytics Operational Dataset (record 148), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J153" t="str">
         <x:v>Medium</x:v>
@@ -5485,7 +5485,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I154" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Workforce Analytics Workflow Platform feeds Workforce Analytics Analytics Mart (record 149) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J154" t="str">
         <x:v>Medium</x:v>
@@ -5517,7 +5517,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I155" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Workforce Analytics Analytics Mart integrates with Workforce Analytics Reporting Workspace (record 150) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J155" t="str">
         <x:v>Medium</x:v>
@@ -5549,7 +5549,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I156" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Workforce Analytics Reporting Workspace depends on Workforce Analytics Workflow Platform (record 151) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J156" t="str">
         <x:v>Medium</x:v>
@@ -5581,7 +5581,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I157" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Workforce Analytics Workflow Platform hosted on Workforce Analytics Primary Midwest Data Center Hosting Segment (record 152) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J157" t="str">
         <x:v>Medium</x:v>
@@ -5613,7 +5613,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I158" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Workforce Analytics Workflow Platform hosted in Primary Midwest Data Center (record 153), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J158" t="str">
         <x:v>Medium</x:v>
@@ -5645,7 +5645,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I159" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks on AWS Lakehouse target for Workforce Analytics Operational Dataset (record 154) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J159" t="str">
         <x:v>Medium</x:v>
@@ -5677,7 +5677,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I160" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Workforce Analytics governed by Human Resources governance council (record 155) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J160" t="str">
         <x:v>Medium</x:v>
@@ -5709,7 +5709,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I161" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate HR / workforce analytics program funded by CHRO (record 156) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J161" t="str">
         <x:v>Medium</x:v>
@@ -5741,7 +5741,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I162" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse replaces candidate legacy Workforce Analytics Operational Dataset (record 157) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J162" t="str">
         <x:v>Medium</x:v>
@@ -5773,7 +5773,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I163" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Workforce Analytics used by Workforce Analytics Analyst / Steward (record 158), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J163" t="str">
         <x:v>Medium</x:v>
@@ -5805,7 +5805,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I164" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Workforce Analytics Operational Dataset part of HR / workforce analytics modernization and readiness program (record 159) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J164" t="str">
         <x:v>Medium</x:v>
@@ -5837,7 +5837,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I165" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Salesforce provides Workforce Analytics Workflow Platform (record 160) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J165" t="str">
         <x:v>Medium</x:v>
@@ -5869,7 +5869,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I166" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Workforce Analytics measured by Workforce Analytics cycle time (record 161) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J166" t="str">
         <x:v>Medium</x:v>
@@ -5901,7 +5901,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01</x:v>
       </x:c>
       <x:c r="I167" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Workforce Analytics has risk Workforce Analytics data lineage and definition risk (record 162) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J167" t="str">
         <x:v>Medium</x:v>
@@ -5933,7 +5933,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I168" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Clinical Quality Analytics Workflow Platform supports Clinical Quality Analytics (record 163), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J168" t="str">
         <x:v>Medium</x:v>
@@ -5965,7 +5965,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I169" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics owned by VP Quality (record 164) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J169" t="str">
         <x:v>Medium</x:v>
@@ -5997,7 +5997,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I170" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics Operational Dataset produced by Clinical Quality Analytics Workflow Platform (record 165) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J170" t="str">
         <x:v>Medium</x:v>
@@ -6029,7 +6029,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I171" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Clinical Quality Analytics Analytics Mart consumes Clinical Quality Analytics Operational Dataset (record 166) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J171" t="str">
         <x:v>Medium</x:v>
@@ -6061,7 +6061,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I172" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Clinical Quality Analytics Workflow Platform feeds Clinical Quality Analytics Analytics Mart (record 167) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J172" t="str">
         <x:v>Medium</x:v>
@@ -6093,7 +6093,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I173" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Clinical Quality Analytics Analytics Mart integrates with Clinical Quality Analytics Reporting Workspace (record 168), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J173" t="str">
         <x:v>Medium</x:v>
@@ -6125,7 +6125,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I174" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics Reporting Workspace depends on Clinical Quality Analytics Workflow Platform (record 169) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J174" t="str">
         <x:v>Medium</x:v>
@@ -6157,7 +6157,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I175" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics Workflow Platform hosted on Clinical Quality Analytics Primary Midwest Data Center Hosting Segment (record 170) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J175" t="str">
         <x:v>Medium</x:v>
@@ -6189,7 +6189,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I176" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Clinical Quality Analytics Workflow Platform hosted in Primary Midwest Data Center (record 171) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J176" t="str">
         <x:v>Medium</x:v>
@@ -6221,7 +6221,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I177" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse target for Clinical Quality Analytics Operational Dataset (record 172) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J177" t="str">
         <x:v>Medium</x:v>
@@ -6253,7 +6253,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I178" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Clinical Quality Analytics governed by Quality and Provider Performance governance council (record 173), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J178" t="str">
         <x:v>Medium</x:v>
@@ -6285,7 +6285,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I179" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Clinical quality analytics program funded by VP Quality (record 174) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J179" t="str">
         <x:v>Medium</x:v>
@@ -6317,7 +6317,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I180" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks on AWS Lakehouse replaces candidate legacy Clinical Quality Analytics Operational Dataset (record 175) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J180" t="str">
         <x:v>Medium</x:v>
@@ -6349,7 +6349,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I181" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Clinical Quality Analytics used by Clinical Quality Analytics Analyst / Steward (record 176) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J181" t="str">
         <x:v>Medium</x:v>
@@ -6381,7 +6381,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I182" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Clinical Quality Analytics Operational Dataset part of Clinical quality analytics modernization and readiness program (record 177) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J182" t="str">
         <x:v>Medium</x:v>
@@ -6413,7 +6413,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I183" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Optum Managed Services provides Clinical Quality Analytics Workflow Platform (record 178), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J183" t="str">
         <x:v>Medium</x:v>
@@ -6445,7 +6445,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I184" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Clinical Quality Analytics measured by Clinical Quality Analytics cycle time (record 179) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J184" t="str">
         <x:v>Medium</x:v>
@@ -6477,7 +6477,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01</x:v>
       </x:c>
       <x:c r="I185" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics has risk Clinical Quality Analytics data lineage and definition risk (record 180) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J185" t="str">
         <x:v>Medium</x:v>
@@ -6509,7 +6509,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I186" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Claims and Payment Analytics Workflow Platform supports Claims and Payment Analytics (record 181) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J186" t="str">
         <x:v>Medium</x:v>
@@ -6541,7 +6541,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I187" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Claims and Payment Analytics owned by VP Claims Analytics (record 182) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J187" t="str">
         <x:v>Medium</x:v>
@@ -6573,7 +6573,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I188" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Claims Payment Analytics Operational Dataset produced by Claims and Payment Analytics Workflow Platform (record 183), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J188" t="str">
         <x:v>Medium</x:v>
@@ -6605,7 +6605,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I189" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Claims and Payment Analytics Analytics Mart consumes Claims Payment Analytics Operational Dataset (record 184) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J189" t="str">
         <x:v>Medium</x:v>
@@ -6637,7 +6637,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I190" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims and Payment Analytics Workflow Platform feeds Claims Payment Analytics Analytics Mart (record 185) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J190" t="str">
         <x:v>Medium</x:v>
@@ -6669,7 +6669,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I191" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Claims and Payment Analytics Analytics Mart integrates with Claims and Payment Analytics Reporting Workspace (record 186) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J191" t="str">
         <x:v>Medium</x:v>
@@ -6701,7 +6701,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I192" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Claims and Payment Analytics Reporting Workspace depends on Claims and Payment Analytics Workflow Platform (record 187) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J192" t="str">
         <x:v>Medium</x:v>
@@ -6733,7 +6733,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I193" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Claims and Payment Analytics Workflow Platform hosted on Claims and Payment Analytics Primary Midwest Data Center Hosting Segment (record 188), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J193" t="str">
         <x:v>Medium</x:v>
@@ -6765,7 +6765,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I194" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Claims and Payment Analytics Workflow Platform hosted in Primary Midwest Data Center (record 189) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J194" t="str">
         <x:v>Medium</x:v>
@@ -6797,7 +6797,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I195" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks on AWS Lakehouse target for Claims Payment Analytics Operational Dataset (record 190) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J195" t="str">
         <x:v>Medium</x:v>
@@ -6829,7 +6829,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I196" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Claims and Payment Analytics governed by Claims Analytics governance council (record 191) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J196" t="str">
         <x:v>Medium</x:v>
@@ -6861,7 +6861,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I197" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Claims analytics program funded by VP Claims Analytics (record 192) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J197" t="str">
         <x:v>Medium</x:v>
@@ -6893,7 +6893,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I198" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Databricks on AWS Lakehouse replaces candidate legacy Claims Payment Analytics Operational Dataset (record 193), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J198" t="str">
         <x:v>Medium</x:v>
@@ -6925,7 +6925,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I199" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Claims and Payment Analytics used by Claims and Payment Analytics Analyst / Steward (record 194) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J199" t="str">
         <x:v>Medium</x:v>
@@ -6957,7 +6957,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I200" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Claims Payment Analytics Operational Dataset part of Claims analytics modernization and readiness program (record 195) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J200" t="str">
         <x:v>Medium</x:v>
@@ -6989,7 +6989,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I201" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks provides Claims and Payment Analytics Workflow Platform (record 196) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J201" t="str">
         <x:v>Medium</x:v>
@@ -7021,7 +7021,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I202" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Claims and Payment Analytics measured by Claims and Payment Analytics cycle time (record 197) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J202" t="str">
         <x:v>Medium</x:v>
@@ -7053,7 +7053,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01</x:v>
       </x:c>
       <x:c r="I203" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Claims and Payment Analytics has risk Claims and Payment Analytics data lineage and definition risk (record 198), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J203" t="str">
         <x:v>Medium</x:v>
@@ -7085,7 +7085,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I204" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Provider Performance Analytics Workflow Platform supports Provider Performance Analytics (record 199) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J204" t="str">
         <x:v>Medium</x:v>
@@ -7117,7 +7117,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I205" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider Performance Analytics owned by VP Provider Performance (record 200) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J205" t="str">
         <x:v>Medium</x:v>
@@ -7149,7 +7149,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I206" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Provider Performance Analytics Operational Dataset produced by Provider Performance Analytics Workflow Platform (record 201) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J206" t="str">
         <x:v>Medium</x:v>
@@ -7181,7 +7181,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I207" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Provider Performance Analytics Analytics Mart consumes Provider Performance Analytics Operational Dataset (record 202) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J207" t="str">
         <x:v>Medium</x:v>
@@ -7213,7 +7213,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I208" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Provider Performance Analytics Workflow Platform feeds Provider Performance Analytics Analytics Mart (record 203), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J208" t="str">
         <x:v>Medium</x:v>
@@ -7245,7 +7245,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I209" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Provider Performance Analytics Analytics Mart integrates with Provider Performance Analytics Reporting Workspace (record 204) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J209" t="str">
         <x:v>Medium</x:v>
@@ -7277,7 +7277,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I210" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider Performance Analytics Reporting Workspace depends on Provider Performance Analytics Workflow Platform (record 205) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J210" t="str">
         <x:v>Medium</x:v>
@@ -7309,7 +7309,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I211" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Provider Performance Analytics Workflow Platform hosted on Provider Performance Analytics Primary Midwest Data Center Hosting Segment (record 206) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J211" t="str">
         <x:v>Medium</x:v>
@@ -7341,7 +7341,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I212" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Provider Performance Analytics Workflow Platform hosted in Primary Midwest Data Center (record 207) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J212" t="str">
         <x:v>Medium</x:v>
@@ -7373,7 +7373,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I213" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Databricks on AWS Lakehouse target for Provider Performance Analytics Operational Dataset (record 208), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J213" t="str">
         <x:v>Medium</x:v>
@@ -7405,7 +7405,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I214" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Provider Performance Analytics governed by Provider Network governance council (record 209) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J214" t="str">
         <x:v>Medium</x:v>
@@ -7437,7 +7437,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I215" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider performance analytics program funded by VP Provider Performance (record 210) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J215" t="str">
         <x:v>Medium</x:v>
@@ -7469,7 +7469,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I216" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse replaces candidate legacy Provider Performance Analytics Operational Dataset (record 211) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J216" t="str">
         <x:v>Medium</x:v>
@@ -7501,7 +7501,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I217" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Provider Performance Analytics used by Provider Performance Analytics Analyst / Steward (record 212) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J217" t="str">
         <x:v>Medium</x:v>
@@ -7533,7 +7533,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I218" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Provider Performance Analytics Operational Dataset part of Provider performance analytics modernization and readiness program (record 213), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J218" t="str">
         <x:v>Medium</x:v>
@@ -7565,7 +7565,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I219" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Microsoft provides Provider Performance Analytics Workflow Platform (record 214) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J219" t="str">
         <x:v>Medium</x:v>
@@ -7597,7 +7597,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I220" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Provider Performance Analytics measured by Provider Performance Analytics cycle time (record 215) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J220" t="str">
         <x:v>Medium</x:v>
@@ -7629,7 +7629,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01</x:v>
       </x:c>
       <x:c r="I221" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Provider Performance Analytics has risk Provider Performance Analytics data lineage and definition risk (record 216) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J221" t="str">
         <x:v>Medium</x:v>
@@ -7661,7 +7661,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I222" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse supports Enterprise Data Platform (record 217) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J222" t="str">
         <x:v>Medium</x:v>
@@ -7693,7 +7693,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I223" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Enterprise Data Platform owned by CDAO (record 218), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J223" t="str">
         <x:v>Medium</x:v>
@@ -7725,7 +7725,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I224" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Enterprise Data Platform Operational Dataset produced by Databricks on AWS Lakehouse (record 219) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J224" t="str">
         <x:v>Medium</x:v>
@@ -7757,7 +7757,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I225" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Netezza Enterprise Warehouse consumes Enterprise Data Platform Operational Dataset (record 220) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J225" t="str">
         <x:v>Medium</x:v>
@@ -7789,7 +7789,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I226" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse feeds Enterprise Data Platform Analytics Mart (record 221) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J226" t="str">
         <x:v>Medium</x:v>
@@ -7821,7 +7821,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I227" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Netezza Enterprise Warehouse integrates with Informatica PowerCenter (record 222) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J227" t="str">
         <x:v>Medium</x:v>
@@ -7853,7 +7853,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I228" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Informatica PowerCenter depends on Databricks on AWS Lakehouse (record 223), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J228" t="str">
         <x:v>Medium</x:v>
@@ -7885,7 +7885,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I229" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks on AWS Lakehouse hosted on Enterprise Data Platform Primary Midwest Data Center Hosting Segment (record 224) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J229" t="str">
         <x:v>Medium</x:v>
@@ -7917,7 +7917,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I230" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks on AWS Lakehouse hosted in Primary Midwest Data Center (record 225) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J230" t="str">
         <x:v>Medium</x:v>
@@ -7949,7 +7949,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I231" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse target for Enterprise Data Platform Operational Dataset (record 226) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J231" t="str">
         <x:v>Medium</x:v>
@@ -7981,7 +7981,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I232" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Enterprise Data Platform governed by Enterprise Data, Analytics &amp; AI governance council (record 227) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J232" t="str">
         <x:v>Medium</x:v>
@@ -8013,7 +8013,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I233" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Enterprise data platform / lakehouse program funded by CDAO (record 228), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J233" t="str">
         <x:v>Medium</x:v>
@@ -8045,7 +8045,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I234" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks on AWS Lakehouse replaces candidate legacy Enterprise Data Platform Operational Dataset (record 229) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J234" t="str">
         <x:v>Medium</x:v>
@@ -8077,7 +8077,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I235" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Enterprise Data Platform used by Enterprise Data Platform Analyst / Steward (record 230) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J235" t="str">
         <x:v>Medium</x:v>
@@ -8109,7 +8109,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I236" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Enterprise Data Platform Operational Dataset part of Enterprise data platform / lakehouse modernization and readiness program (record 231) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J236" t="str">
         <x:v>Medium</x:v>
@@ -8141,7 +8141,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I237" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Genesys provides Databricks on AWS Lakehouse (record 232) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J237" t="str">
         <x:v>Medium</x:v>
@@ -8173,7 +8173,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I238" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Enterprise Data Platform measured by Enterprise Data Platform cycle time (record 233), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J238" t="str">
         <x:v>Medium</x:v>
@@ -8205,7 +8205,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01</x:v>
       </x:c>
       <x:c r="I239" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Enterprise Data Platform has risk Enterprise Data Platform data lineage and definition risk (record 234) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J239" t="str">
         <x:v>Medium</x:v>
@@ -8237,7 +8237,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I240" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Data Governance and Data Quality Workflow Platform supports Data Governance and Data Quality (record 235) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J240" t="str">
         <x:v>Medium</x:v>
@@ -8269,7 +8269,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I241" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Data Governance and Data Quality owned by Chief Data Officer (record 236) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J241" t="str">
         <x:v>Medium</x:v>
@@ -8301,7 +8301,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I242" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Data Governance Data Quality Operational Dataset produced by Data Governance and Data Quality Workflow Platform (record 237) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J242" t="str">
         <x:v>Medium</x:v>
@@ -8333,7 +8333,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I243" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Data Governance and Data Quality Analytics Mart consumes Data Governance Data Quality Operational Dataset (record 238), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J243" t="str">
         <x:v>Medium</x:v>
@@ -8365,7 +8365,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I244" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Data Governance and Data Quality Workflow Platform feeds Data Governance Data Quality Analytics Mart (record 239) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J244" t="str">
         <x:v>Medium</x:v>
@@ -8397,7 +8397,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I245" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Data Governance and Data Quality Analytics Mart integrates with Data Governance and Data Quality Reporting Workspace (record 240) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J245" t="str">
         <x:v>Medium</x:v>
@@ -8429,7 +8429,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I246" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Data Governance and Data Quality Reporting Workspace depends on Data Governance and Data Quality Workflow Platform (record 241) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J246" t="str">
         <x:v>Medium</x:v>
@@ -8461,7 +8461,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I247" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Data Governance and Data Quality Workflow Platform hosted on Data Governance and Data Quality Primary Midwest Data Center Hosting Segment (record 242) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J247" t="str">
         <x:v>Medium</x:v>
@@ -8493,7 +8493,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I248" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Data Governance and Data Quality Workflow Platform hosted in Primary Midwest Data Center (record 243), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J248" t="str">
         <x:v>Medium</x:v>
@@ -8525,7 +8525,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I249" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks on AWS Lakehouse target for Data Governance Data Quality Operational Dataset (record 244) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J249" t="str">
         <x:v>Medium</x:v>
@@ -8557,7 +8557,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I250" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Data Governance and Data Quality governed by Data Governance governance council (record 245) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J250" t="str">
         <x:v>Medium</x:v>
@@ -8589,7 +8589,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I251" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Data governance, quality, catalog, MDM program funded by Chief Data Officer (record 246) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J251" t="str">
         <x:v>Medium</x:v>
@@ -8621,7 +8621,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I252" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse replaces candidate legacy Data Governance Data Quality Operational Dataset (record 247) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J252" t="str">
         <x:v>Medium</x:v>
@@ -8653,7 +8653,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I253" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Data Governance and Data Quality used by Data Governance and Data Quality Analyst / Steward (record 248), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J253" t="str">
         <x:v>Medium</x:v>
@@ -8685,7 +8685,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I254" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Data Governance Data Quality Operational Dataset part of Data governance, quality, catalog, MDM modernization and readiness program (record 249) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J254" t="str">
         <x:v>Medium</x:v>
@@ -8717,7 +8717,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I255" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Salesforce provides Data Governance and Data Quality Workflow Platform (record 250) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J255" t="str">
         <x:v>Medium</x:v>
@@ -8749,7 +8749,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I256" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Data Governance and Data Quality measured by Data Governance and Data Quality cycle time (record 251) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J256" t="str">
         <x:v>Medium</x:v>
@@ -8781,7 +8781,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01</x:v>
       </x:c>
       <x:c r="I257" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Data Governance and Data Quality has risk Data Governance and Data Quality data lineage and definition risk (record 252) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J257" t="str">
         <x:v>Medium</x:v>
@@ -8807,13 +8807,13 @@
         <x:v>Business Function</x:v>
       </x:c>
       <x:c r="G258" t="str">
-        <x:v>Agent Assist and Next Best Action Workflow Platform supports agent assist, call summarization, intent detection, guided resolution.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="H258" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.</x:v>
       </x:c>
       <x:c r="I258" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action Workflow Platform supports Agent Assist and Next Best Action (record 253) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J258" t="str">
         <x:v>Medium</x:v>
@@ -8839,13 +8839,13 @@
         <x:v>Owner / Executive Role</x:v>
       </x:c>
       <x:c r="G259" t="str">
-        <x:v>VP Contact Center is accountable for Agent Assist and Next Best Action evidence and readiness.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="H259" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Knowledge article export with duplicate and stale article flags.</x:v>
       </x:c>
       <x:c r="I259" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action owned by VP Contact Center (record 254) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J259" t="str">
         <x:v>Medium</x:v>
@@ -8871,13 +8871,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G260" t="str">
-        <x:v>Agent Assist Next Best Action Operational Dataset is produced or sourced from Agent Assist and Next Best Action Workflow Platform.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="H260" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="I260" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist Next Best Action Operational Dataset produced by Agent Assist and Next Best Action Workflow Platform (record 255) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J260" t="str">
         <x:v>Medium</x:v>
@@ -8903,13 +8903,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G261" t="str">
-        <x:v>Agent Assist and Next Best Action Analytics Mart consumes Agent Assist Next Best Action Operational Dataset for analytics/workflow support.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="H261" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.</x:v>
       </x:c>
       <x:c r="I261" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action Analytics Mart consumes Agent Assist Next Best Action Operational Dataset (record 256) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J261" t="str">
         <x:v>Medium</x:v>
@@ -8935,13 +8935,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G262" t="str">
-        <x:v>Agent Assist and Next Best Action Workflow Platform feeds Agent Assist Next Best Action Analytics Mart through batch/API/interface flows that require lineage validation.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="H262" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.</x:v>
       </x:c>
       <x:c r="I262" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action Workflow Platform feeds Agent Assist Next Best Action Analytics Mart (record 257) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J262" t="str">
         <x:v>Medium</x:v>
@@ -8967,13 +8967,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G263" t="str">
-        <x:v>Agent Assist and Next Best Action Analytics Mart integrates with Agent Assist and Next Best Action Reporting Workspace for workflow, reporting, or exception handling.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="H263" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.</x:v>
       </x:c>
       <x:c r="I263" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action Analytics Mart integrates with Agent Assist and Next Best Action Reporting Workspace (record 258) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J263" t="str">
         <x:v>Medium</x:v>
@@ -8999,13 +8999,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G264" t="str">
-        <x:v>Agent Assist and Next Best Action Reporting Workspace depends on Agent Assist and Next Best Action Workflow Platform for source data, workflow handoff, or identity/transaction context.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="H264" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Knowledge article export with duplicate and stale article flags.</x:v>
       </x:c>
       <x:c r="I264" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action Reporting Workspace depends on Agent Assist and Next Best Action Workflow Platform (record 259) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J264" t="str">
         <x:v>Medium</x:v>
@@ -9031,13 +9031,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G265" t="str">
-        <x:v>Agent Assist and Next Best Action Workflow Platform is hosted on or materially depends on the Agent Assist and Next Best Action hosting segment.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="H265" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="I265" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action Workflow Platform hosted on Agent Assist and Next Best Action Primary Midwest Data Center Hosting Segment (record 260) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J265" t="str">
         <x:v>Medium</x:v>
@@ -9063,13 +9063,13 @@
         <x:v>Infrastructure / Platform</x:v>
       </x:c>
       <x:c r="G266" t="str">
-        <x:v>Agent Assist and Next Best Action Workflow Platform has current or dependent hosting in Primary Midwest Data Center.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="H266" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.</x:v>
       </x:c>
       <x:c r="I266" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action Workflow Platform hosted in Primary Midwest Data Center (record 261) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J266" t="str">
         <x:v>Medium</x:v>
@@ -9095,13 +9095,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G267" t="str">
-        <x:v>Databricks on AWS Lakehouse is the target path for governed modernization of Agent Assist Next Best Action Operational Dataset.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="H267" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.</x:v>
       </x:c>
       <x:c r="I267" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse target for Agent Assist Next Best Action Operational Dataset (record 262) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J267" t="str">
         <x:v>Medium</x:v>
@@ -9127,13 +9127,13 @@
         <x:v>Governance Forum</x:v>
       </x:c>
       <x:c r="G268" t="str">
-        <x:v>Member Experience governance council should validate evidence, exceptions, metrics, and promotion readiness.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="H268" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.</x:v>
       </x:c>
       <x:c r="I268" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action governed by Member Experience governance council (record 263) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J268" t="str">
         <x:v>Medium</x:v>
@@ -9159,13 +9159,13 @@
         <x:v>Owner / Executive Role</x:v>
       </x:c>
       <x:c r="G269" t="str">
-        <x:v>VP Contact Center sponsors or funds the Agent Assist for member service modernization and readiness program.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="H269" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Knowledge article export with duplicate and stale article flags.</x:v>
       </x:c>
       <x:c r="I269" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist for member service program funded by VP Contact Center (record 264) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J269" t="str">
         <x:v>Medium</x:v>
@@ -9191,13 +9191,13 @@
         <x:v>Data Asset</x:v>
       </x:c>
       <x:c r="G270" t="str">
-        <x:v>Agent Assist Next Best Action Operational Dataset is a candidate legacy/fragmented asset to be rationalized or certified through Databricks on AWS Lakehouse.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="H270" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="I270" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse replaces candidate legacy Agent Assist Next Best Action Operational Dataset (record 265) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J270" t="str">
         <x:v>Medium</x:v>
@@ -9223,13 +9223,13 @@
         <x:v>Workforce Role</x:v>
       </x:c>
       <x:c r="G271" t="str">
-        <x:v>Agent Assist and Next Best Action analysts and stewards use this context for reporting, reconciliation, and readiness checks.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Agents search Salesforce cases, benefits notes, prior-auth status, and claims inquiry screens separately while the member waits on the call.</x:v>
       </x:c>
       <x:c r="H271" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.</x:v>
       </x:c>
       <x:c r="I271" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action used by Agent Assist and Next Best Action Analyst / Steward (record 266) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J271" t="str">
         <x:v>Medium</x:v>
@@ -9255,13 +9255,13 @@
         <x:v>Program / Initiative</x:v>
       </x:c>
       <x:c r="G272" t="str">
-        <x:v>Agent Assist Next Best Action Operational Dataset is in scope for Agent Assist for member service modernization, validation, or context-readiness work.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Call transcript intent labels are inconsistent across billing, eligibility, claims status, and prior authorization categories.</x:v>
       </x:c>
       <x:c r="H272" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.</x:v>
       </x:c>
       <x:c r="I272" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist Next Best Action Operational Dataset part of Agent Assist for member service modernization and readiness program (record 267) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J272" t="str">
         <x:v>Medium</x:v>
@@ -9287,13 +9287,13 @@
         <x:v>System / Platform</x:v>
       </x:c>
       <x:c r="G273" t="str">
-        <x:v>Tableau provides, supports, or contracts around Agent Assist and Next Best Action Workflow Platform.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Genesys call metadata and Salesforce case outcomes are not reliably joined to claims and benefits context.</x:v>
       </x:c>
       <x:c r="H273" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.</x:v>
       </x:c>
       <x:c r="I273" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Tableau provides Agent Assist and Next Best Action Workflow Platform (record 268) against Agent Assist / Member Service evidence: intent taxonomy drift; confirm audited Claude agent-assist answer packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J273" t="str">
         <x:v>Medium</x:v>
@@ -9319,13 +9319,13 @@
         <x:v>Metric / Outcome</x:v>
       </x:c>
       <x:c r="G274" t="str">
-        <x:v>Agent Assist and Next Best Action cycle time measures Agent Assist and Next Best Action performance.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Knowledge articles are duplicated across operations playbooks and CRM snippets, creating conflicting guidance for appeal and denial inquiries.</x:v>
       </x:c>
       <x:c r="H274" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Knowledge article export with duplicate and stale article flags.</x:v>
       </x:c>
       <x:c r="I274" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action measured by Agent Assist and Next Best Action cycle time (record 269) against Agent Assist / Member Service evidence: CRM-to-claims join gaps; confirm Genesys-Salesforce-claims context join owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J274" t="str">
         <x:v>Medium</x:v>
@@ -9351,13 +9351,13 @@
         <x:v>Risk / Control</x:v>
       </x:c>
       <x:c r="G275" t="str">
-        <x:v>Agent Assist and Next Best Action has a known evidence/lineage risk until validation is complete.</x:v>
+        <x:v>Agent Assist / Member Service relationship: Supervisors cannot prove whether AI suggestions reduce handle time without a baseline for after-call work, transfer rate, and first-contact resolution.</x:v>
       </x:c>
       <x:c r="H275" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01</x:v>
+        <x:v>Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="I275" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action has risk Agent Assist and Next Best Action data lineage and definition risk (record 270) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="J275" t="str">
         <x:v>Medium</x:v>
@@ -9389,7 +9389,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I276" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Epic Clarity supports Unified Clinical and Claims Lakehouse (record 271) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J276" t="str">
         <x:v>Medium</x:v>
@@ -9421,7 +9421,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I277" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Unified Clinical and Claims Lakehouse owned by CDAO (record 272) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J277" t="str">
         <x:v>Medium</x:v>
@@ -9453,7 +9453,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I278" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Unified Clinical Claims Lakehouse Operational Dataset produced by Epic Clarity (record 273), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J278" t="str">
         <x:v>Medium</x:v>
@@ -9485,7 +9485,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I279" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Claims Administration Platform consumes Unified Clinical Claims Lakehouse Operational Dataset (record 274) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J279" t="str">
         <x:v>Medium</x:v>
@@ -9517,7 +9517,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I280" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Epic Clarity feeds Unified Clinical Claims Lakehouse Analytics Mart (record 275) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J280" t="str">
         <x:v>Medium</x:v>
@@ -9549,7 +9549,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I281" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Claims Administration Platform integrates with Pharmacy Claims Platform (record 276) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J281" t="str">
         <x:v>Medium</x:v>
@@ -9581,7 +9581,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I282" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Pharmacy Claims Platform depends on Epic Clarity (record 277) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J282" t="str">
         <x:v>Medium</x:v>
@@ -9613,7 +9613,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I283" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Epic Clarity hosted on Unified Clinical and Claims Lakehouse Primary Midwest Data Center Hosting Segment (record 278), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J283" t="str">
         <x:v>Medium</x:v>
@@ -9645,7 +9645,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I284" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Epic Clarity hosted in Primary Midwest Data Center (record 279) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J284" t="str">
         <x:v>Medium</x:v>
@@ -9677,7 +9677,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I285" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks on AWS Lakehouse target for Unified Clinical Claims Lakehouse Operational Dataset (record 280) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J285" t="str">
         <x:v>Medium</x:v>
@@ -9709,7 +9709,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I286" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse governed by Enterprise Data, Analytics &amp; AI governance council (record 281) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J286" t="str">
         <x:v>Medium</x:v>
@@ -9741,7 +9741,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I287" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Unified clinical + claims lakehouse program funded by CDAO (record 282) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J287" t="str">
         <x:v>Medium</x:v>
@@ -9773,7 +9773,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I288" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Databricks on AWS Lakehouse replaces candidate legacy Unified Clinical Claims Lakehouse Operational Dataset (record 283), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J288" t="str">
         <x:v>Medium</x:v>
@@ -9805,7 +9805,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I289" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Unified Clinical and Claims Lakehouse used by Unified Clinical and Claims Lakehouse Analyst / Steward (record 284) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J289" t="str">
         <x:v>Medium</x:v>
@@ -9837,7 +9837,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I290" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Unified Clinical Claims Lakehouse Operational Dataset part of Unified clinical + claims lakehouse modernization and readiness program (record 285) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J290" t="str">
         <x:v>Medium</x:v>
@@ -9869,7 +9869,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I291" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Epic provides Epic Clarity (record 286) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J291" t="str">
         <x:v>Medium</x:v>
@@ -9901,7 +9901,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I292" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Unified Clinical and Claims Lakehouse measured by Unified Clinical and Claims Lakehouse cycle time (record 287) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J292" t="str">
         <x:v>Medium</x:v>
@@ -9933,7 +9933,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01</x:v>
       </x:c>
       <x:c r="I293" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Unified Clinical and Claims Lakehouse has risk Unified Clinical and Claims Lakehouse data lineage and definition risk (record 288), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J293" t="str">
         <x:v>Medium</x:v>
@@ -9965,7 +9965,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I294" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline Workflow Platform supports IT Budget and Tower Baseline (record 289) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J294" t="str">
         <x:v>Medium</x:v>
@@ -9997,7 +9997,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I295" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget and Tower Baseline owned by CIO / CFO (record 290) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J295" t="str">
         <x:v>Medium</x:v>
@@ -10029,7 +10029,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I296" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate IT Budget Tower Baseline Operational Dataset produced by IT Budget and Tower Baseline Workflow Platform (record 291) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J296" t="str">
         <x:v>Medium</x:v>
@@ -10061,7 +10061,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I297" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline Analytics Mart consumes IT Budget Tower Baseline Operational Dataset (record 292) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J297" t="str">
         <x:v>Medium</x:v>
@@ -10093,7 +10093,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I298" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for IT Budget and Tower Baseline Workflow Platform feeds IT Budget Tower Baseline Analytics Mart (record 293), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J298" t="str">
         <x:v>Medium</x:v>
@@ -10125,7 +10125,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I299" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline Analytics Mart integrates with IT Budget and Tower Baseline Reporting Workspace (record 294) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J299" t="str">
         <x:v>Medium</x:v>
@@ -10157,7 +10157,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I300" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget and Tower Baseline Reporting Workspace depends on IT Budget and Tower Baseline Workflow Platform (record 295) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J300" t="str">
         <x:v>Medium</x:v>
@@ -10189,7 +10189,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I301" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate IT Budget and Tower Baseline Workflow Platform hosted on IT Budget and Tower Baseline Primary Midwest Data Center Hosting Segment (record 296) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J301" t="str">
         <x:v>Medium</x:v>
@@ -10221,7 +10221,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I302" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline Workflow Platform hosted in Primary Midwest Data Center (record 297) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J302" t="str">
         <x:v>Medium</x:v>
@@ -10253,7 +10253,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I303" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Databricks on AWS Lakehouse target for IT Budget Tower Baseline Operational Dataset (record 298), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J303" t="str">
         <x:v>Medium</x:v>
@@ -10285,7 +10285,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I304" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline governed by Technology Finance governance council (record 299) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J304" t="str">
         <x:v>Medium</x:v>
@@ -10317,7 +10317,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I305" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT budget and Tower spend baseline program funded by CIO / CFO (record 300) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J305" t="str">
         <x:v>Medium</x:v>
@@ -10349,7 +10349,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I306" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse replaces candidate legacy IT Budget Tower Baseline Operational Dataset (record 301) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J306" t="str">
         <x:v>Medium</x:v>
@@ -10381,7 +10381,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I307" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline used by IT Budget and Tower Baseline Analyst / Steward (record 302) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J307" t="str">
         <x:v>Medium</x:v>
@@ -10413,7 +10413,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I308" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for IT Budget Tower Baseline Operational Dataset part of IT budget and Tower spend baseline modernization and readiness program (record 303), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J308" t="str">
         <x:v>Medium</x:v>
@@ -10445,7 +10445,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I309" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Optum Managed Services provides IT Budget and Tower Baseline Workflow Platform (record 304) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J309" t="str">
         <x:v>Medium</x:v>
@@ -10477,7 +10477,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I310" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for IT Budget and Tower Baseline measured by IT Budget and Tower Baseline cycle time (record 305) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J310" t="str">
         <x:v>Medium</x:v>
@@ -10509,7 +10509,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01</x:v>
       </x:c>
       <x:c r="I311" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate IT Budget and Tower Baseline has risk IT Budget and Tower Baseline data lineage and definition risk (record 306) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J311" t="str">
         <x:v>Medium</x:v>
@@ -10541,7 +10541,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I312" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Vendor and Contract Optimization Workflow Platform supports Vendor and Contract Optimization (record 307) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J312" t="str">
         <x:v>Medium</x:v>
@@ -10573,7 +10573,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I313" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization owned by Chief Procurement Officer (record 308), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J313" t="str">
         <x:v>Medium</x:v>
@@ -10605,7 +10605,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I314" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Vendor Contract Optimization Operational Dataset produced by Vendor and Contract Optimization Workflow Platform (record 309) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J314" t="str">
         <x:v>Medium</x:v>
@@ -10637,7 +10637,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I315" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization Analytics Mart consumes Vendor Contract Optimization Operational Dataset (record 310) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J315" t="str">
         <x:v>Medium</x:v>
@@ -10669,7 +10669,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I316" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Vendor and Contract Optimization Workflow Platform feeds Vendor Contract Optimization Analytics Mart (record 311) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J316" t="str">
         <x:v>Medium</x:v>
@@ -10701,7 +10701,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I317" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Vendor and Contract Optimization Analytics Mart integrates with Vendor and Contract Optimization Reporting Workspace (record 312) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J317" t="str">
         <x:v>Medium</x:v>
@@ -10733,7 +10733,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I318" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization Reporting Workspace depends on Vendor and Contract Optimization Workflow Platform (record 313), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J318" t="str">
         <x:v>Medium</x:v>
@@ -10765,7 +10765,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I319" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization Workflow Platform hosted on Vendor and Contract Optimization Primary Midwest Data Center Hosting Segment (record 314) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J319" t="str">
         <x:v>Medium</x:v>
@@ -10797,7 +10797,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I320" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization Workflow Platform hosted in Primary Midwest Data Center (record 315) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J320" t="str">
         <x:v>Medium</x:v>
@@ -10829,7 +10829,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I321" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Databricks on AWS Lakehouse target for Vendor Contract Optimization Operational Dataset (record 316) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J321" t="str">
         <x:v>Medium</x:v>
@@ -10861,7 +10861,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I322" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Vendor and Contract Optimization governed by Procurement and Vendor Management governance council (record 317) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J322" t="str">
         <x:v>Medium</x:v>
@@ -10893,7 +10893,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I323" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Vendor / contract / sourcing context program funded by Chief Procurement Officer (record 318), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J323" t="str">
         <x:v>Medium</x:v>
@@ -10925,7 +10925,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I324" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks on AWS Lakehouse replaces candidate legacy Vendor Contract Optimization Operational Dataset (record 319) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J324" t="str">
         <x:v>Medium</x:v>
@@ -10957,7 +10957,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I325" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization used by Vendor and Contract Optimization Analyst / Steward (record 320) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J325" t="str">
         <x:v>Medium</x:v>
@@ -10989,7 +10989,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I326" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Vendor Contract Optimization Operational Dataset part of Vendor / contract / sourcing context modernization and readiness program (record 321) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J326" t="str">
         <x:v>Medium</x:v>
@@ -11021,7 +11021,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I327" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Oracle provides Vendor and Contract Optimization Workflow Platform (record 322) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J327" t="str">
         <x:v>Medium</x:v>
@@ -11053,7 +11053,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I328" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization measured by Vendor and Contract Optimization cycle time (record 323), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J328" t="str">
         <x:v>Medium</x:v>
@@ -11085,7 +11085,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01</x:v>
       </x:c>
       <x:c r="I329" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization has risk Vendor and Contract Optimization data lineage and definition risk (record 324) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J329" t="str">
         <x:v>Medium</x:v>
@@ -11117,7 +11117,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I330" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for ServiceNow CMDB supports Infrastructure and CMDB (record 325) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J330" t="str">
         <x:v>Medium</x:v>
@@ -11149,7 +11149,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I331" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Infrastructure and CMDB owned by CTO (record 326) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J331" t="str">
         <x:v>Medium</x:v>
@@ -11181,7 +11181,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I332" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Infrastructure CMDB Operational Dataset produced by ServiceNow CMDB (record 327) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J332" t="str">
         <x:v>Medium</x:v>
@@ -11213,7 +11213,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I333" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for VMware Data Center Cluster consumes Infrastructure CMDB Operational Dataset (record 328), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J333" t="str">
         <x:v>Medium</x:v>
@@ -11245,7 +11245,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I334" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile ServiceNow CMDB feeds Infrastructure CMDB Analytics Mart (record 329) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J334" t="str">
         <x:v>Medium</x:v>
@@ -11277,7 +11277,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I335" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for VMware Data Center Cluster integrates with AWS Analytics Landing Zone (record 330) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J335" t="str">
         <x:v>Medium</x:v>
@@ -11309,7 +11309,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I336" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate AWS Analytics Landing Zone depends on ServiceNow CMDB (record 331) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J336" t="str">
         <x:v>Medium</x:v>
@@ -11341,7 +11341,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I337" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm ServiceNow CMDB hosted on Infrastructure and CMDB Primary Midwest Data Center Hosting Segment (record 332) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J337" t="str">
         <x:v>Medium</x:v>
@@ -11373,7 +11373,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I338" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for ServiceNow CMDB hosted in Primary Midwest Data Center (record 333), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J338" t="str">
         <x:v>Medium</x:v>
@@ -11405,7 +11405,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I339" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Databricks on AWS Lakehouse target for Infrastructure CMDB Operational Dataset (record 334) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J339" t="str">
         <x:v>Medium</x:v>
@@ -11437,7 +11437,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I340" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Infrastructure and CMDB governed by Technology Operations governance council (record 335) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J340" t="str">
         <x:v>Medium</x:v>
@@ -11469,7 +11469,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I341" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate CMDB / infrastructure / cloud inventory context program funded by CTO (record 336) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J341" t="str">
         <x:v>Medium</x:v>
@@ -11501,7 +11501,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I342" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse replaces candidate legacy Infrastructure CMDB Operational Dataset (record 337) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J342" t="str">
         <x:v>Medium</x:v>
@@ -11533,7 +11533,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I343" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Infrastructure and CMDB used by Infrastructure and CMDB Analyst / Steward (record 338), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J343" t="str">
         <x:v>Medium</x:v>
@@ -11565,7 +11565,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I344" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Infrastructure CMDB Operational Dataset part of CMDB / infrastructure / cloud inventory context modernization and readiness program (record 339) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J344" t="str">
         <x:v>Medium</x:v>
@@ -11597,7 +11597,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I345" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for AWS provides ServiceNow CMDB (record 340) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J345" t="str">
         <x:v>Medium</x:v>
@@ -11629,7 +11629,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I346" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Infrastructure and CMDB measured by Infrastructure and CMDB cycle time (record 341) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J346" t="str">
         <x:v>Medium</x:v>
@@ -11661,7 +11661,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01</x:v>
       </x:c>
       <x:c r="I347" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Infrastructure and CMDB has risk Infrastructure and CMDB data lineage and definition risk (record 342) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J347" t="str">
         <x:v>Medium</x:v>
@@ -11693,7 +11693,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I348" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for ServiceNow ITSM supports Incident Problem Change Operations (record 343), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J348" t="str">
         <x:v>Medium</x:v>
@@ -11725,7 +11725,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I349" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations owned by VP IT Operations (record 344) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J349" t="str">
         <x:v>Medium</x:v>
@@ -11757,7 +11757,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I350" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations Operational Dataset produced by ServiceNow ITSM (record 345) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J350" t="str">
         <x:v>Medium</x:v>
@@ -11789,7 +11789,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I351" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Datadog Observability consumes Incident Problem Change Operations Operational Dataset (record 346) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J351" t="str">
         <x:v>Medium</x:v>
@@ -11821,7 +11821,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I352" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm ServiceNow ITSM feeds Incident Problem Change Operations Analytics Mart (record 347) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J352" t="str">
         <x:v>Medium</x:v>
@@ -11853,7 +11853,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I353" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Datadog Observability integrates with PagerDuty Incident Response (record 348), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J353" t="str">
         <x:v>Medium</x:v>
@@ -11885,7 +11885,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I354" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile PagerDuty Incident Response depends on ServiceNow ITSM (record 349) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J354" t="str">
         <x:v>Medium</x:v>
@@ -11917,7 +11917,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I355" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for ServiceNow ITSM hosted on Incident Problem Change Operations Primary Midwest Data Center Hosting Segment (record 350) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J355" t="str">
         <x:v>Medium</x:v>
@@ -11949,7 +11949,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I356" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate ServiceNow ITSM hosted in Primary Midwest Data Center (record 351) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J356" t="str">
         <x:v>Medium</x:v>
@@ -11981,7 +11981,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I357" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Databricks on AWS Lakehouse target for Incident Problem Change Operations Operational Dataset (record 352) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J357" t="str">
         <x:v>Medium</x:v>
@@ -12013,7 +12013,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I358" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations governed by Technology Operations governance council (record 353), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J358" t="str">
         <x:v>Medium</x:v>
@@ -12045,7 +12045,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I359" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Incident / problem / change operational health context program funded by VP IT Operations (record 354) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J359" t="str">
         <x:v>Medium</x:v>
@@ -12077,7 +12077,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I360" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Databricks on AWS Lakehouse replaces candidate legacy Incident Problem Change Operations Operational Dataset (record 355) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J360" t="str">
         <x:v>Medium</x:v>
@@ -12109,7 +12109,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I361" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Validate Incident Problem Change Operations used by Incident Problem Change Operations Analyst / Steward (record 356) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for relationships.</x:v>
       </x:c>
       <x:c r="J361" t="str">
         <x:v>Medium</x:v>
@@ -12141,7 +12141,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I362" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm Incident Problem Change Operations Operational Dataset part of Incident / problem / change operational health context modernization and readiness program (record 357) current-vs-target status, module boundary, volume baseline, and relationship links before this relationships record is used downstream.</x:v>
       </x:c>
       <x:c r="J362" t="str">
         <x:v>Medium</x:v>
@@ -12173,7 +12173,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I363" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Attach client evidence for Optum Managed Services provides ServiceNow ITSM (record 358), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="J363" t="str">
         <x:v>Medium</x:v>
@@ -12205,7 +12205,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I364" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Reconcile Incident Problem Change Operations measured by Incident Problem Change Operations cycle time (record 359) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="J364" t="str">
         <x:v>Medium</x:v>
@@ -12237,7 +12237,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01</x:v>
       </x:c>
       <x:c r="I365" t="str">
-        <x:v>Relationship is synthetic candidate; validate source lineage and owner attestation before promotion.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations has risk Incident Problem Change Operations data lineage and definition risk (record 360) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="J365" t="str">
         <x:v>Medium</x:v>
@@ -12264,7 +12264,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7edfbaa21954e3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5be7c057e5741f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12339,7 +12339,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcc4c939d05848f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d15dce8957e4fec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12633,7 +12633,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R199f32c7dce541f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f69fbeb48924aa6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12711,7 +12711,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f08880d01f044d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc332d6f1021e4de0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12821,7 +12821,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cd48164eaa141d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra630c55421854b2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13017,7 +13017,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf93d0c45b704ef0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84e3285d649d4cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>